--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484764_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484764_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4538</v>
+        <v>8.1309</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9205</v>
+        <v>5.9149</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5334</v>
+        <v>2.2159</v>
       </c>
       <c r="G2" t="n">
         <v>3.7103</v>
@@ -610,13 +610,13 @@
         <v>3.0192</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5208</v>
+        <v>0.1562</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5161</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9953</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.2452</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4489</v>
+        <v>3.9078</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9599</v>
+        <v>1.8368</v>
       </c>
       <c r="F3" t="n">
-        <v>1.489</v>
+        <v>2.071</v>
       </c>
       <c r="G3" t="n">
         <v>1.7797</v>
@@ -688,13 +688,13 @@
         <v>2.8305</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8024</v>
+        <v>-0.3435</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.6337</v>
+        <v>-0.7568</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1687</v>
+        <v>0.4133</v>
       </c>
       <c r="V3" t="n">
         <v>1.528</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4246</v>
+        <v>1.0996</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.3694</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5219</v>
+        <v>1.469</v>
       </c>
       <c r="G4" t="n">
         <v>0.4227</v>
@@ -766,13 +766,13 @@
         <v>2.8305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3791</v>
+        <v>0.0541</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1851</v>
+        <v>-0.0871</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1941</v>
+        <v>0.1412</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2642</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3584</v>
+        <v>0.2255</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2415</v>
+        <v>-1.1867</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1168</v>
+        <v>1.4122</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0451</v>
+        <v>-2.9977</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7755</v>
+        <v>-0.7396</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8206</v>
+        <v>-2.2582</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0623</v>
+        <v>-2.3692</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0211</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0411</v>
+        <v>-1.8253</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0172</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7967</v>
+        <v>-0.1956</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7795</v>
+        <v>-0.4329</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0641</v>
+        <v>-0.041</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1793</v>
+        <v>0.2582</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2433</v>
+        <v>-0.2992</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.5094</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1318</v>
+        <v>0.001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1481</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2799</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9977</v>
+        <v>0.0451</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7396</v>
+        <v>-0.7755</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.2582</v>
+        <v>0.8206</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.3692</v>
+        <v>0.0623</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5439000000000001</v>
+        <v>0.0211</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8253</v>
+        <v>0.0411</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.0172</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1956</v>
+        <v>-0.7967</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4329</v>
+        <v>0.7795</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6983</v>
+        <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1346</v>
+        <v>-0.4215</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2968</v>
+        <v>-0.1517</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4315</v>
+        <v>-0.2698</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5094</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8678</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>J. ANDREU TARIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.143</v>
+        <v>-0.9036</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9253</v>
+        <v>-1.1929</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7823</v>
+        <v>0.2893</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6174</v>
+        <v>-1.1511</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4268</v>
+        <v>-1.123</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1906</v>
+        <v>-0.0281</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2103</v>
+        <v>-1.1123</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7776</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5673</v>
+        <v>-0.5262</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5928</v>
+        <v>-0.0388</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3507</v>
+        <v>-0.5369</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7579</v>
+        <v>0.4981</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.774</v>
+        <v>0.5661</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.661</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.887</v>
+        <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6172</v>
+        <v>-0.3186</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9028</v>
+        <v>-0.0806</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7143</v>
+        <v>-0.238</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ANDREU TARIN</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1875</v>
+        <v>-1.4122</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5826</v>
+        <v>-2.0357</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3951</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1511</v>
+        <v>2.6174</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.123</v>
+        <v>2.4268</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0281</v>
+        <v>0.1906</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1123</v>
+        <v>3.2103</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5862000000000001</v>
+        <v>3.7776</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5262</v>
+        <v>-0.5673</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0388</v>
+        <v>-0.5928</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5369</v>
+        <v>-1.3507</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4981</v>
+        <v>0.7579</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5661</v>
+        <v>-3.774</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.661</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5661</v>
+        <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6025</v>
+        <v>0.348</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4703</v>
+        <v>-0.2076</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1322</v>
+        <v>0.5556</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1563</v>
+        <v>-5.1877</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7029</v>
+        <v>-3.6318</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4535</v>
+        <v>-1.5559</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.9398</v>
+        <v>-3.3891</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.3761</v>
+        <v>-0.3083</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5636</v>
+        <v>-3.0808</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.9562</v>
+        <v>-0.6358</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4572</v>
+        <v>2.4886</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4989</v>
+        <v>-3.1244</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9836</v>
+        <v>-2.7533</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9189</v>
+        <v>-2.797</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.0437</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7548</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7548</v>
+        <v>2.0757</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9341</v>
+        <v>-0.4023</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2533</v>
+        <v>-0.7691</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6808</v>
+        <v>0.3669</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9054</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9054</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3498</v>
+        <v>-5.2924</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8468</v>
+        <v>-3.839</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.503</v>
+        <v>-1.4535</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3891</v>
+        <v>-5.9398</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3083</v>
+        <v>-3.3761</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0808</v>
+        <v>-2.5636</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6358</v>
+        <v>-3.9562</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4886</v>
+        <v>-1.4572</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.1244</v>
+        <v>-2.4989</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7533</v>
+        <v>-1.9836</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.797</v>
+        <v>-1.9189</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0437</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7548</v>
+        <v>0.7548</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0757</v>
+        <v>0.7548</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5644</v>
+        <v>0.798</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9842</v>
+        <v>0.1172</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4198</v>
+        <v>0.6808</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.9054</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2452</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="11">
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.01910000000000078</v>
+        <v>0.568900000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.181</v>
+        <v>-4.5932</v>
       </c>
       <c r="F11" t="n">
         <v>5.1619</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.902499999999999</v>
+        <v>-4.9025</v>
       </c>
       <c r="H11" t="n">
         <v>-3.819</v>
@@ -1312,13 +1312,13 @@
         <v>16.0395</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7584</v>
+        <v>-0.1706</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.787</v>
+        <v>-2.1992</v>
       </c>
       <c r="U11" t="n">
-        <v>2.0286</v>
+        <v>2.0287</v>
       </c>
       <c r="V11" t="n">
         <v>1.8678</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.1983</v>
+        <v>4.0293</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4495</v>
+        <v>1.8649</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7488</v>
+        <v>2.1644</v>
       </c>
       <c r="G12" t="n">
         <v>3.1214</v>
@@ -1390,13 +1390,13 @@
         <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6772</v>
+        <v>0.5082</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1234</v>
+        <v>-0.4612</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5538</v>
+        <v>0.9695</v>
       </c>
       <c r="V12" t="n">
         <v>1.1545</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1113</v>
+        <v>3.0042</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3553</v>
+        <v>2.063</v>
       </c>
       <c r="F13" t="n">
-        <v>0.756</v>
+        <v>0.9412</v>
       </c>
       <c r="G13" t="n">
         <v>1.9632</v>
@@ -1468,13 +1468,13 @@
         <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5255</v>
+        <v>0.4184</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5443</v>
+        <v>0.252</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0188</v>
+        <v>0.1664</v>
       </c>
       <c r="V13" t="n">
         <v>0.6226</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2774</v>
+        <v>2.0616</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7439</v>
+        <v>1.1337</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5335</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>1.5877</v>
@@ -1624,13 +1624,13 @@
         <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1445</v>
+        <v>-0.3603</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0582</v>
+        <v>-0.6684</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0864</v>
+        <v>0.3081</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7033</v>
+        <v>0.9692</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1676</v>
+        <v>0.1247</v>
       </c>
       <c r="F16" t="n">
-        <v>0.871</v>
+        <v>0.8445</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6379</v>
@@ -1702,13 +1702,13 @@
         <v>2.0757</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1722</v>
+        <v>0.0936</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5726</v>
+        <v>-0.2803</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4004</v>
+        <v>0.374</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3736</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARREÑO</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.317</v>
+        <v>0.7496</v>
       </c>
       <c r="E17" t="n">
-        <v>0.317</v>
+        <v>0.6533</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.0963</v>
       </c>
       <c r="G17" t="n">
-        <v>0.317</v>
+        <v>0.2593</v>
       </c>
       <c r="H17" t="n">
-        <v>0.317</v>
+        <v>0.4148</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.1555</v>
       </c>
       <c r="J17" t="n">
-        <v>0.317</v>
+        <v>0.7271</v>
       </c>
       <c r="K17" t="n">
-        <v>0.317</v>
+        <v>1.2944</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.5673</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.4678</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.8796</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.4118</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.4571</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.5077</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.0506</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3736</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>A. VALDERRAMA CARREÑO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1744</v>
+        <v>0.317</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1264</v>
+        <v>0.317</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0479</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5488</v>
+        <v>0.317</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1199</v>
+        <v>0.317</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4289</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4047</v>
+        <v>0.317</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0886</v>
+        <v>0.317</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3162</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.856</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0313</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8873</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.6983</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3239</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2504</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0735</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1661</v>
+        <v>0.2008</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3773</v>
+        <v>0.1264</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5434</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1943</v>
+        <v>1.5488</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3289</v>
+        <v>1.1199</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1346</v>
+        <v>0.4289</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5565</v>
+        <v>2.4047</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2146</v>
+        <v>1.0886</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6581</v>
+        <v>1.3162</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3623</v>
+        <v>-0.856</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1143</v>
+        <v>0.0313</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4765</v>
+        <v>-0.8873</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1887</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1887</v>
+        <v>1.1322</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1716</v>
+        <v>0.3504</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1793</v>
+        <v>0.2504</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0076</v>
+        <v>0.1</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1307</v>
+        <v>0.0061</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4584</v>
+        <v>-0.6696</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5891999999999999</v>
+        <v>0.6756</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2593</v>
+        <v>-0.1943</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4148</v>
+        <v>-1.3289</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1555</v>
+        <v>1.1346</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7271</v>
+        <v>-0.5565</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2944</v>
+        <v>-1.2146</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5673</v>
+        <v>0.6581</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4678</v>
+        <v>0.3623</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8796</v>
+        <v>-0.1143</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4118</v>
+        <v>0.4765</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3374</v>
+        <v>0.0116</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7026</v>
+        <v>-0.113</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6348</v>
+        <v>0.1247</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3736</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1539</v>
+        <v>-0.101</v>
       </c>
       <c r="E21" t="n">
         <v>-0.0377</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1162</v>
+        <v>-0.0633</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1303</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0235</v>
+        <v>0.0294</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0353</v>
+        <v>0.0882</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9832</v>
+        <v>-0.9675</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1671</v>
+        <v>-3.0697</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1839</v>
+        <v>2.1022</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5222</v>
@@ -2170,13 +2170,13 @@
         <v>2.2644</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4221</v>
+        <v>0.4378</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5726</v>
+        <v>-0.4752</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9948</v>
+        <v>0.913</v>
       </c>
       <c r="V22" t="n">
         <v>0.8716</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2742</v>
+        <v>-2.4233</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4985</v>
+        <v>-2.3036</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2243</v>
+        <v>-0.1197</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1596</v>
@@ -2248,13 +2248,13 @@
         <v>0.1887</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8289</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0465</v>
+        <v>0.1484</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8754</v>
+        <v>0.5314</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2452</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2555</v>
+        <v>-3.6007</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9401</v>
+        <v>-3.2324</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3154</v>
+        <v>-0.3683</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3143</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5308</v>
+        <v>0.1856</v>
       </c>
       <c r="T24" t="n">
-        <v>0.532</v>
+        <v>0.2397</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0012</v>
+        <v>-0.0541</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6415999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6497</v>
+        <v>-6.0952</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9429</v>
+        <v>-4.6506</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7068</v>
+        <v>-1.4446</v>
       </c>
       <c r="G25" t="n">
         <v>-3.4549</v>
@@ -2404,13 +2404,13 @@
         <v>0.9435</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.044</v>
+        <v>-0.4895</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.3544</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3974</v>
+        <v>-0.1352</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2072</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01929999999999854</v>
+        <v>0.6688000000000009</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.162</v>
+        <v>-5.161899999999997</v>
       </c>
       <c r="F26" t="n">
-        <v>5.1812</v>
+        <v>5.8306</v>
       </c>
       <c r="G26" t="n">
         <v>4.9026</v>
       </c>
       <c r="H26" t="n">
-        <v>3.818999999999999</v>
+        <v>3.819</v>
       </c>
       <c r="I26" t="n">
-        <v>1.083499999999999</v>
+        <v>1.083499999999998</v>
       </c>
       <c r="J26" t="n">
         <v>9.548400000000001</v>
@@ -2482,13 +2482,13 @@
         <v>12.2655</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7584</v>
+        <v>1.408</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.0286</v>
+        <v>-2.0285</v>
       </c>
       <c r="U26" t="n">
-        <v>2.787</v>
+        <v>3.4366</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8679</v>
